--- a/artfynd/A 51820-2023 artfynd.xlsx
+++ b/artfynd/A 51820-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51820-2023 artfynd.xlsx
+++ b/artfynd/A 51820-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104020672</v>
+        <v>104020611</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549211.9294425522</v>
+        <v>549174</v>
       </c>
       <c r="R2" t="n">
-        <v>6984459.64135565</v>
+        <v>6984442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104020676</v>
+        <v>104020632</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549228.3418086888</v>
+        <v>549217</v>
       </c>
       <c r="R3" t="n">
-        <v>6984428.062712368</v>
+        <v>6984441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104020632</v>
+        <v>104020678</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,12 +927,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549217.2248886311</v>
+        <v>549223</v>
       </c>
       <c r="R4" t="n">
-        <v>6984440.625444559</v>
+        <v>6984438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104020674</v>
+        <v>104020646</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,39 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Åsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549426.938206105</v>
+        <v>549297</v>
       </c>
       <c r="R5" t="n">
-        <v>6984482.445930548</v>
+        <v>6984473</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,15 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104020629</v>
+        <v>104020676</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1204,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549224.7757765203</v>
+        <v>549229</v>
       </c>
       <c r="R6" t="n">
-        <v>6984423.007501826</v>
+        <v>6984428</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,37 +1255,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104020646</v>
+        <v>104020672</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549296.8575930971</v>
+        <v>549212</v>
       </c>
       <c r="R7" t="n">
-        <v>6984473.655566128</v>
+        <v>6984460</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,37 +1371,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104020678</v>
+        <v>104020609</v>
       </c>
       <c r="B8" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1446,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549223.6387966376</v>
+        <v>549186</v>
       </c>
       <c r="R8" t="n">
-        <v>6984437.994329248</v>
+        <v>6984447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,15 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104020599</v>
+        <v>104020638</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1567,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549201.5950923124</v>
+        <v>549403</v>
       </c>
       <c r="R9" t="n">
-        <v>6984420.384088265</v>
+        <v>6984499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,50 +1603,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104020609</v>
+        <v>104020674</v>
       </c>
       <c r="B10" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Åsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549186.1619451878</v>
+        <v>549427</v>
       </c>
       <c r="R10" t="n">
-        <v>6984447.431074126</v>
+        <v>6984482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,248 +1717,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>104020638</v>
-      </c>
-      <c r="B11" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Åsbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>549402.5582701635</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6984498.898620511</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>104020611</v>
-      </c>
-      <c r="B12" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>53</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Åsbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>549174.4023900917</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6984442.252289029</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 51820-2023 artfynd.xlsx
+++ b/artfynd/A 51820-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020611</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020632</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020678</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020646</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020676</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020672</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020609</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020638</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,8 +1766,24 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020674</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>